--- a/xls/square_un_16_tri3_20.xlsx
+++ b/xls/square_un_16_tri3_20.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>340</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>435</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>2388</v>
+      </c>
+      <c r="I18">
+        <v>-0.00016969770784458211</v>
+      </c>
+      <c r="J18">
+        <v>-0.7304513936923035</v>
+      </c>
+      <c r="K18">
+        <v>2.2845354973486343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>564</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>340</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>485</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2676</v>
+      </c>
+      <c r="I19">
+        <v>-0.00010748099921078721</v>
+      </c>
+      <c r="J19">
+        <v>-0.35605591433174894</v>
+      </c>
+      <c r="K19">
+        <v>3.0393129144966595</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
       </c>
       <c r="B20">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-2.434395220685979</v>
+        <v>-3.9638618133701216e-7</v>
       </c>
       <c r="J20">
-        <v>-2.1810511002666013</v>
+        <v>-0.0007677938904799562</v>
       </c>
       <c r="K20">
-        <v>0.13516980697421987</v>
+        <v>2.7660809781480182</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-2.4037413053745116</v>
+        <v>-1.1335264611198908e-7</v>
       </c>
       <c r="J21">
-        <v>-1.9075316433702305</v>
+        <v>-0.0002280642598698848</v>
       </c>
       <c r="K21">
-        <v>0.737163525554679</v>
+        <v>2.5986810783749603</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.2184949605189181</v>
+        <v>-1.9114271444387576e-8</v>
       </c>
       <c r="J22">
-        <v>-1.1371179867748715</v>
+        <v>-3.631021120049833e-5</v>
       </c>
       <c r="K22">
-        <v>1.8041086887752285</v>
+        <v>2.2172129984656728</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-0.24756097872755845</v>
+        <v>-8.574460666833706e-9</v>
       </c>
       <c r="J23">
-        <v>-0.23509438813358208</v>
+        <v>-1.635281036330107e-5</v>
       </c>
       <c r="K23">
-        <v>3.4662645488369535</v>
+        <v>2.04783725776751</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-0.0010831587995424332</v>
+        <v>-7.285810322116839e-9</v>
       </c>
       <c r="J24">
-        <v>-0.001459692945796971</v>
+        <v>-1.3562930366851896e-5</v>
       </c>
       <c r="K24">
-        <v>3.070562124391605</v>
+        <v>2.006898925928125</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.0004058665503151925</v>
+        <v>-4.689898654228509e-9</v>
       </c>
       <c r="J25">
-        <v>-0.0004895978854049613</v>
+        <v>-8.947403849904956e-6</v>
       </c>
       <c r="K25">
-        <v>2.83405396646354</v>
+        <v>1.919995206279399</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.00020716475438810596</v>
+        <v>-4.228199487975651e-9</v>
       </c>
       <c r="J26">
-        <v>-0.0002544337085044375</v>
+        <v>-7.90437224613239e-6</v>
       </c>
       <c r="K26">
-        <v>2.698174984446041</v>
+        <v>1.891871127107807</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.0001301679787797604</v>
+        <v>-3.2428142833578635e-9</v>
       </c>
       <c r="J27">
-        <v>-0.0001520171026401249</v>
+        <v>-6.375467682361942e-6</v>
       </c>
       <c r="K27">
-        <v>2.578923684793025</v>
+        <v>1.8514551729363946</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-8.158448403064342e-5</v>
+        <v>-3.0183795519404478e-9</v>
       </c>
       <c r="J28">
-        <v>-9.641829645076865e-5</v>
+        <v>-5.94343109191825e-6</v>
       </c>
       <c r="K28">
-        <v>2.4793811780924386</v>
+        <v>1.8357419194971183</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-6.130844717853383e-5</v>
+        <v>-2.7472657296443652e-9</v>
       </c>
       <c r="J29">
-        <v>-7.183914244600386e-5</v>
+        <v>-5.323633822113957e-6</v>
       </c>
       <c r="K29">
-        <v>2.412241488156961</v>
+        <v>1.8114116259864288</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-4.769808529858914e-5</v>
+        <v>-2.1384786605616433e-9</v>
       </c>
       <c r="J30">
-        <v>-5.495524937831673e-5</v>
+        <v>-4.158094112936887e-6</v>
       </c>
       <c r="K30">
-        <v>2.3518223260375217</v>
+        <v>1.757281002366317</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-3.916069395884883e-5</v>
+        <v>-1.650105909895934e-9</v>
       </c>
       <c r="J31">
-        <v>-4.41338371092377e-5</v>
+        <v>-3.2624048211877253e-6</v>
       </c>
       <c r="K31">
-        <v>2.3011483512972326</v>
+        <v>1.7074620853031035</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-3.234694082180584e-5</v>
+        <v>-1.7129011307552016e-9</v>
       </c>
       <c r="J32">
-        <v>-3.615010474404426e-5</v>
+        <v>-3.393450887566507e-6</v>
       </c>
       <c r="K32">
-        <v>2.2549005897738867</v>
+        <v>1.7158280926188856</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_20.xlsx
+++ b/xls/square_un_16_tri3_20.xlsx
@@ -482,13 +482,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-0.00016969770784458211</v>
+        <v>-1.8261941601762621</v>
       </c>
       <c r="J18">
-        <v>-0.7304513936923035</v>
+        <v>-1.9727763970856527</v>
       </c>
       <c r="K18">
-        <v>2.2845354973486343</v>
+        <v>-0.5088610607242887</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.00010748099921078721</v>
+        <v>-1.995497794145894</v>
       </c>
       <c r="J19">
-        <v>-0.35605591433174894</v>
+        <v>-1.6509086472646657</v>
       </c>
       <c r="K19">
-        <v>3.0393129144966595</v>
+        <v>0.6267735693259461</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-3.9638618133701216e-7</v>
+        <v>-0.6187388178432004</v>
       </c>
       <c r="J20">
-        <v>-0.0007677938904799562</v>
+        <v>-0.5380079417413444</v>
       </c>
       <c r="K20">
-        <v>2.7660809781480182</v>
+        <v>2.069301420395905</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.1335264611198908e-7</v>
+        <v>-0.11112795630853135</v>
       </c>
       <c r="J21">
-        <v>-0.0002280642598698848</v>
+        <v>-0.09981241987985308</v>
       </c>
       <c r="K21">
-        <v>2.5986810783749603</v>
+        <v>2.8115888339312036</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.9114271444387576e-8</v>
+        <v>-7.004245748906748e-5</v>
       </c>
       <c r="J22">
-        <v>-3.631021120049833e-5</v>
+        <v>-6.547866456717592e-5</v>
       </c>
       <c r="K22">
-        <v>2.2172129984656728</v>
+        <v>2.3400376117267263</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-8.574460666833706e-9</v>
+        <v>-2.3997491515519584e-5</v>
       </c>
       <c r="J23">
-        <v>-1.635281036330107e-5</v>
+        <v>-2.2333449278988993e-5</v>
       </c>
       <c r="K23">
-        <v>2.04783725776751</v>
+        <v>2.107278247840843</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-7.285810322116839e-9</v>
+        <v>-2.4123302977360668e-5</v>
       </c>
       <c r="J24">
-        <v>-1.3562930366851896e-5</v>
+        <v>-2.0846369139442415e-5</v>
       </c>
       <c r="K24">
-        <v>2.006898925928125</v>
+        <v>2.0701004281067</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-4.689898654228509e-9</v>
+        <v>-1.2163769935607778e-5</v>
       </c>
       <c r="J25">
-        <v>-8.947403849904956e-6</v>
+        <v>-1.1222227283662497e-5</v>
       </c>
       <c r="K25">
-        <v>1.919995206279399</v>
+        <v>1.9544691422406542</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-4.228199487975651e-9</v>
+        <v>-9.366206810473404e-6</v>
       </c>
       <c r="J26">
-        <v>-7.90437224613239e-6</v>
+        <v>-8.966659395499693e-6</v>
       </c>
       <c r="K26">
-        <v>1.891871127107807</v>
+        <v>1.916156722029643</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.2428142833578635e-9</v>
+        <v>-7.88217865640236e-6</v>
       </c>
       <c r="J27">
-        <v>-6.375467682361942e-6</v>
+        <v>-7.4135168118877815e-6</v>
       </c>
       <c r="K27">
-        <v>1.8514551729363946</v>
+        <v>1.8710506307501775</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-3.0183795519404478e-9</v>
+        <v>-8.694934089990586e-6</v>
       </c>
       <c r="J28">
-        <v>-5.94343109191825e-6</v>
+        <v>-7.757120571186648e-6</v>
       </c>
       <c r="K28">
-        <v>1.8357419194971183</v>
+        <v>1.8634325234031184</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -867,13 +867,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-2.7472657296443652e-9</v>
+        <v>-7.5803199864987435e-6</v>
       </c>
       <c r="J29">
-        <v>-5.323633822113957e-6</v>
+        <v>-6.736034697284913e-6</v>
       </c>
       <c r="K29">
-        <v>1.8114116259864288</v>
+        <v>1.8342404788723576</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -902,13 +902,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.1384786605616433e-9</v>
+        <v>-5.42720156699638e-6</v>
       </c>
       <c r="J30">
-        <v>-4.158094112936887e-6</v>
+        <v>-4.955573893922528e-6</v>
       </c>
       <c r="K30">
-        <v>1.757281002366317</v>
+        <v>1.772366416332714</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -937,13 +937,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.650105909895934e-9</v>
+        <v>-4.445816977686825e-6</v>
       </c>
       <c r="J31">
-        <v>-3.2624048211877253e-6</v>
+        <v>-4.005797593997133e-6</v>
       </c>
       <c r="K31">
-        <v>1.7074620853031035</v>
+        <v>1.7244349011054636</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -972,13 +972,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.7129011307552016e-9</v>
+        <v>-4.348200585102855e-6</v>
       </c>
       <c r="J32">
-        <v>-3.393450887566507e-6</v>
+        <v>-4.012320919687039e-6</v>
       </c>
       <c r="K32">
-        <v>1.7158280926188856</v>
+        <v>1.7320100692102598</v>
       </c>
     </row>
   </sheetData>
